--- a/AAII_Financials/Quarterly/ING_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ING_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="92">
   <si>
     <t>ING</t>
   </si>
@@ -656,265 +656,271 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="22" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="31" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="23" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="32" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6859400</v>
+      </c>
+      <c r="E8" s="3">
         <v>9580800</v>
       </c>
-      <c r="E8" s="3">
-        <v>7597200</v>
-      </c>
       <c r="F8" s="3">
+        <v>6346400</v>
+      </c>
+      <c r="G8" s="3">
         <v>3872000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7423100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>988200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5262000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18248400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3973300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5989600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5262000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5958300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18439300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3600900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12863500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3705300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11266000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3648500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11343900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3586100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10611300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3455200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13155300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3953000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16436000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4323000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17117800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4166400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>17356700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3876600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>14795600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3737600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>24540200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3915700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>24780300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3934600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>25747500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3973300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1029,47 +1035,50 @@
       <c r="AN9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6859400</v>
+      </c>
+      <c r="E10" s="3">
         <v>9580800</v>
       </c>
-      <c r="E10" s="3">
-        <v>7597200</v>
-      </c>
       <c r="F10" s="3">
+        <v>6346400</v>
+      </c>
+      <c r="G10" s="3">
         <v>3872000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7423100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>988200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5262000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>18248400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3973300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5989600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5262000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5958300</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1145,8 +1154,11 @@
       <c r="AN10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1187,8 +1199,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1303,8 +1316,11 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1419,47 +1435,50 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E14" s="3">
         <v>455300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3">
+        <v>-61100</v>
+      </c>
+      <c r="G14" s="3">
         <v>551800</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>320300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-19700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>963900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>62800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>-19700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>75000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1535,68 +1554,71 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E15" s="3">
         <v>60200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>193800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>55900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>177300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>59400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>179000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>62300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>74300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>61700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>179000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>63300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-392100</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3">
         <v>-388500</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="3">
         <v>-451000</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3">
         <v>-442200</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1609,50 +1631,53 @@
       <c r="Z15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-468100</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-455300</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-314700</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-280000</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>-280500</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL15" s="3">
         <v>-278300</v>
       </c>
-      <c r="AL15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM15" s="3">
+      <c r="AM15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN15" s="3">
         <v>-313400</v>
       </c>
-      <c r="AN15" s="3" t="s">
+      <c r="AO15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1690,240 +1715,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3491400</v>
+      </c>
+      <c r="E17" s="3">
         <v>3562500</v>
       </c>
-      <c r="E17" s="3">
-        <v>3564300</v>
-      </c>
       <c r="F17" s="3">
+        <v>3624200</v>
+      </c>
+      <c r="G17" s="3">
         <v>3067600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3051500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3108500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2809000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2785200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2557400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2956200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2809000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3336600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11567800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>435500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6671100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1070900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4352700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>42000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4232000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>227600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4631900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>486800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7772700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>746300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9417500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>338100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9427700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>863700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9952900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>338900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8148300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>634600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>17436800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>244600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>18266000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>712500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>18325500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>387400</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3368000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6018300</v>
       </c>
-      <c r="E18" s="3">
-        <v>4032900</v>
-      </c>
       <c r="F18" s="3">
+        <v>2722300</v>
+      </c>
+      <c r="G18" s="3">
         <v>804400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4371600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2120300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2453100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15463200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1416000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3033400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2453100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2621700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6871600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3165400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6192400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2634400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6913300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3606500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7111900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3358400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5979400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2968400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5382500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3206600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7018500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3984900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>7690100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3302700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7403800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3537700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6647300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3102900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>7103300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3671200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>6514300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3222100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>7422000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3586000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1964,8 +1996,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2002,202 +2035,208 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-3448000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1674000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3569000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1909600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3385600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1534600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3379300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1865000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3734300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1718800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3682900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2058300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3226700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1643900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3471600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1410300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3723800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1185100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2555000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1216600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2965400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1432800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2497500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1283000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-4063700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1381600</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3491900</v>
+      </c>
+      <c r="E21" s="3">
         <v>6078500</v>
       </c>
-      <c r="E21" s="3">
-        <v>4226700</v>
-      </c>
       <c r="F21" s="3">
+        <v>2916000</v>
+      </c>
+      <c r="G21" s="3">
         <v>860300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4548900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2060900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2632100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15525500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1490200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3095100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2632100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2685000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4211100</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>4431800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>3072000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>4259900</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>4675000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>3979300</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>4385400</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>4429600</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="3">
         <v>4308400</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN21" s="3">
         <v>3682200</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AO21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2234,8 +2273,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2312,240 +2351,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3334900</v>
+      </c>
+      <c r="E23" s="3">
         <v>5563000</v>
       </c>
-      <c r="E23" s="3">
-        <v>4032900</v>
-      </c>
       <c r="F23" s="3">
+        <v>2783300</v>
+      </c>
+      <c r="G23" s="3">
         <v>252600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4371600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2440600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2472700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14499300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1353200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3033400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2472700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2546700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3423600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1491400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2623400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>724800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3527700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2072000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3732600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1493400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2245100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1249600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1699600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1148300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3791700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2341000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4218600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1892400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3680000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2352500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4092200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1886400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4137900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2238400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4016700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1939100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3358300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2204400</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1030500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1471200</v>
       </c>
-      <c r="E24" s="3">
-        <v>1071100</v>
-      </c>
       <c r="F24" s="3">
+        <v>743400</v>
+      </c>
+      <c r="G24" s="3">
         <v>75600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1226800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-760500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>641900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4252400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>418700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>864700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>641900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>776800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1108700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>461500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>787800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>210500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>945300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>561100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1063300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>448100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>691200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>403700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>603300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>371500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1134700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>665200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1156400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>529900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1190000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>644600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1121100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>508400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1412600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>667600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1146700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>535300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>851000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>612700</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2660,240 +2708,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2304400</v>
+      </c>
+      <c r="E26" s="3">
         <v>4091800</v>
       </c>
-      <c r="E26" s="3">
-        <v>2961800</v>
-      </c>
       <c r="F26" s="3">
+        <v>2039900</v>
+      </c>
+      <c r="G26" s="3">
         <v>177000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3144800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1680100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1830800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10246900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>934500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2168700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1830800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1769900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2314900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1029900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1835600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>514300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2582300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1510900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2669300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1045300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1553900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>845900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1096400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>776800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2657000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1675800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3062200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1362500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2490000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1707900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2971200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1378000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2725300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1570800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2870100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1403900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2507300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1591700</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2224400</v>
+      </c>
+      <c r="E27" s="3">
         <v>4000200</v>
       </c>
-      <c r="E27" s="3">
-        <v>2889000</v>
-      </c>
       <c r="F27" s="3">
+        <v>1967100</v>
+      </c>
+      <c r="G27" s="3">
         <v>99400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3083700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1755300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1763100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10195600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>960000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2097800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1763100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1728600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2289400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1058000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1747500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>465500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2506400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1472100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2606900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1025900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1512100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>817900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1057100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>756500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2597500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1646400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3006900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1337400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2423800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1717900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2914100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1345100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2682700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1543900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2820700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1379200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2465000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1582300</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3008,8 +3065,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3079,53 +3139,56 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-858400</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL29" s="3">
-        <v>0</v>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>-1200</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3240,8 +3303,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3356,8 +3422,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3394,202 +3463,208 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>3448000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1674000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3569000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1909600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3385600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1534600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3379300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1865000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3734300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1718800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3682900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2058300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3226700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1643900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3471600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1410300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3723800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1185100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2555000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1216600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2965400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1432800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2497500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1283000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>4063700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1381600</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2224400</v>
+      </c>
+      <c r="E33" s="3">
         <v>4000200</v>
       </c>
-      <c r="E33" s="3">
-        <v>2889000</v>
-      </c>
       <c r="F33" s="3">
+        <v>1967100</v>
+      </c>
+      <c r="G33" s="3">
         <v>99400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3083700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1755300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1763100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10195600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>960000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2097800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1763100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1728600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2289400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1058000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1747500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>465500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2506400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1472100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2606900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1025900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1512100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>817900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1057100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>756500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2597500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1646400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3006900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1337400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2423800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>859500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2914100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1345100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2682700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1543900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2820700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1379200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2463800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1583500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3704,245 +3779,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2224400</v>
+      </c>
+      <c r="E35" s="3">
         <v>4000200</v>
       </c>
-      <c r="E35" s="3">
-        <v>2889000</v>
-      </c>
       <c r="F35" s="3">
+        <v>1967100</v>
+      </c>
+      <c r="G35" s="3">
         <v>99400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3083700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1755300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1763100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10195600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>960000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2097800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1763100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1728600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2289400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1058000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1747500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>465500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2506400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1472100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2606900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1025900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1512100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>817900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1057100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>756500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2597500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1646400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3006900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1337400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2423800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>859500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2914100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1345100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2682700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1543900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2820700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1379200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2463800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1583500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3983,8 +4067,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4025,279 +4110,286 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>85553500</v>
+      </c>
+      <c r="E41" s="3">
         <v>11835200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>106172600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6861000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>118381000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10520600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>124056800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16703000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>132466200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>123544700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>124056800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>128207300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>135922500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>174352600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>162122500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>170946100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>141054400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>165421500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>156085700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>146725700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>136096200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>145409800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>163238300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>109316100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>103126700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>111646800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>102058600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>95107500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>95115800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>78999600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>76753500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>68427400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>56997100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>57475100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>51478000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>83719700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>55171400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>60478200</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>197639700</v>
+      </c>
+      <c r="E42" s="3">
         <v>156879200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>172319400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>140094200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>80761800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>130397900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>94845000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>116074600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>73259500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>75164100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>94845000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>65391100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>126719400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>170173500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>151716000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>140200400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>111439000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>136758800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>129383900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>124093600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>104154500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1000</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z42" s="3">
+      <c r="Z42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA42" s="3">
         <v>134976000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>112289700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>149430400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>139906900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>144563200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>142522900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>153060400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>169496100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>171616300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>138252700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>158238700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>160605000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>160267300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>143314000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>168886600</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>466100</v>
+      </c>
+      <c r="E43" s="3">
         <v>537700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>574300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>502100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>430700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>343800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>309000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>373000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>309000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>407400</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -4373,8 +4465,11 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4411,8 +4506,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4489,46 +4584,49 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>5561800</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3">
         <v>4210600</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>4890000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>6172900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>24300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -4605,47 +4703,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>283659300</v>
+      </c>
+      <c r="E46" s="3">
         <v>235823600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>279066400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>223229100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>199573600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>244599300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>219210700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>231552800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>205725600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>198733100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>219210700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>194005900</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4721,356 +4822,368 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>159885800</v>
+      </c>
+      <c r="E47" s="3">
         <v>135664000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>133020600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>107750300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>184021200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>106644200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>178284900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>93775800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>159362600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>173669600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>178284900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>177498900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1661400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1591900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1607100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1616700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1720500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1583000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1545700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1533200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1471200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1522600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1936400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1911600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2089700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1765200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1549300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1514400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1423000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1223900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1188000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1194600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1220700</v>
-      </c>
-      <c r="AJ47" s="3">
-        <v>1196000</v>
       </c>
       <c r="AK47" s="3">
         <v>1196000</v>
       </c>
       <c r="AL47" s="3">
+        <v>1196000</v>
+      </c>
+      <c r="AM47" s="3">
         <v>1385100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1339300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1153900</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3028700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2909500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2839700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2519900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2609000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2651700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2647400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2614100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2451500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2501100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2647400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2691200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2709200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2701800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2787700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2755900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2726500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2751500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2783600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2780700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2833600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3100200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3366500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3521700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3703000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3797500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3323300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3492900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2026300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1962700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2008200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1961000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2093600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2115000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2247300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2335900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2350000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2422700</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1987900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1772900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1654700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1381100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1334000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1324200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1222700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1177700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1084500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1219300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1222700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1203800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1220600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1195300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1217600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1232600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1253200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1341800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1391300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1390300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1390400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1471700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1730200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2164500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2236800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2375300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2255200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2223700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2175400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1939400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1959900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1912700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1648200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1677400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1672900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1733700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1741900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1905100</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5185,8 +5298,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5301,124 +5417,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13593100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2829600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10903100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2553100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8986400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2492500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11565500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2894100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12733900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10579000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11565500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9438300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1989200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R52" s="3">
         <v>1683300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>1037500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1475400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2184800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>528800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>771000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>879300</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>852200</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
       <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
         <v>2194000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1457000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3111000</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>1663500</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>1525900</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL52" s="3">
         <v>1028900</v>
       </c>
-      <c r="AL52" s="3">
-        <v>0</v>
-      </c>
       <c r="AM52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="3">
         <v>1083400</v>
       </c>
-      <c r="AN52" s="3" t="s">
+      <c r="AO52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5533,124 +5655,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1326127000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1244956000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1281237800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1060002100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1122479400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1083562500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1132603700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1043960700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1038272200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1081315600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1132603700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1110591000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1071954100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1144277600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1109931600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1093595400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1031293500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1064786000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1034984300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1001272100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>934838100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>992731600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1074374000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1066643800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1041030900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1129919800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1074512000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1082483200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1049267800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>998595500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>994770400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>973948000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>949445900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>966819900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>967212600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1038604700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>991964500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1021850900</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5691,8 +5819,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5733,47 +5862,48 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>919531600</v>
+      </c>
+      <c r="E57" s="3">
         <v>868721400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>891273000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>733392700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>764034100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>744482100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>774170300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>745357500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>741441500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>730725000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>774170300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>776184300</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -5816,125 +5946,128 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>2759700</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>2660500</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>6961900</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL57" s="3">
         <v>6210200</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM57" s="3">
+      <c r="AM57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN57" s="3">
         <v>5157700</v>
       </c>
-      <c r="AN57" s="3" t="s">
+      <c r="AO57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1436100</v>
+      </c>
+      <c r="E58" s="3">
         <v>154100000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2934800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>124762400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1771100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>132905900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2554600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>122370400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5416700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>53493900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2554600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>47035000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>40386400</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>41139400</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>26943800</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>63998200</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>60482300</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>56683700</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5947,8 +6080,8 @@
       <c r="AH58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
@@ -5965,163 +6098,169 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>30658100</v>
+      </c>
+      <c r="E59" s="3">
         <v>4520400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31410500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10289900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>36564900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16808900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>44355900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10025600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>54148900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>44355900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>649700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>360000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>304700</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>293800</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>306800</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>341100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>422200</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>646700</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>572900</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>1707400</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>1944400</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL59" s="3">
         <v>1493400</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN59" s="3">
         <v>1221900</v>
       </c>
-      <c r="AN59" s="3" t="s">
+      <c r="AO59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>951625700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1029261500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>925618300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>870187400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>802370100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>895700200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>821080800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>878820100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>801007100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>784218900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>821080800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>823869000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6197,240 +6336,249 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>297974400</v>
+      </c>
+      <c r="E61" s="3">
         <v>136436500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>272718700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>121654400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>240403900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>111238000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>228991300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>87679800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>168482100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>225521800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>228991300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>212655400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>83336900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>114967000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>118163300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>125316400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>76484300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>116550700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>112815600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>106701200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>70671800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>116623600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>86367300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>159713500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>99012700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>166510400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>101439800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>162318400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>157887600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>147800400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>145291800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>137794600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>125723500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>121291600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>129374400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>152360500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>141393600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>147367200</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17404300</v>
+      </c>
+      <c r="E62" s="3">
         <v>11843400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18636500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11118100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18183900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13322600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17093900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13525700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18116300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15973800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17093900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17020900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1449800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R62" s="3">
         <v>1718100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>1732400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2210900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3803500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>1271700</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>1444400</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>1614500</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>1832800</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>2540900</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>2864700</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>3397400</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL62" s="3">
         <v>3513000</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN62" s="3">
         <v>4070800</v>
       </c>
-      <c r="AN62" s="3" t="s">
+      <c r="AO62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6545,8 +6693,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6661,8 +6812,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6777,124 +6931,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1267419200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1179982400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1218617700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1004408300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1063007600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1022074700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1069815500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>983039400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>987605400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1025714400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1069815500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1053796200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1016674900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1088846300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1053754100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1035575000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>972841000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1005083700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>975501400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>945086200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>880343100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>936472300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1015132100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1005295300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>978260400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1064369300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1012635700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1019338200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>989020300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>944326500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>939889100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>918866800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>892890900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>910978500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>911466500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>979044400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>933517000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>963813000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6935,8 +7095,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7051,8 +7212,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7167,8 +7331,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7283,8 +7450,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7399,124 +7569,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>40167900</v>
+      </c>
+      <c r="E72" s="3">
         <v>46983700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>44979400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>37522500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>41874000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>44544000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>45096100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>44392400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3">
         <v>45096100</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P72" s="3">
         <v>42695800</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R72" s="3">
         <v>42793900</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>44157600</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>42771800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>39769300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38325100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>39131900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>40171700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>41237000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>41854000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>42788900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>40428200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>41431600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>39271100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>35291500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>32281200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>35245800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>32536600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>34190400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>31707400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>35526500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>31583700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>33312700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7631,8 +7807,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7747,8 +7926,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7863,124 +8045,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>57404300</v>
+      </c>
+      <c r="E76" s="3">
         <v>63500100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>61409300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>54563600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>58597400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>60444300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>62001100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>60382600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>50296100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>54737500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>62001100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>56148400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>55279200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>55431300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>56177500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>58020400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>58452500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>59702300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>59482900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>56185900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>54494900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>56259400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>59241900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>61348500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>62770500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>65550400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>61876300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>63145000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>60247500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>54269100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>54881300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>55081200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>56555000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>55841400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>55746100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>59560300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>58447500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>58037900</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8095,245 +8283,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2224400</v>
+      </c>
+      <c r="E81" s="3">
         <v>4000200</v>
       </c>
-      <c r="E81" s="3">
-        <v>2889000</v>
-      </c>
       <c r="F81" s="3">
+        <v>1967100</v>
+      </c>
+      <c r="G81" s="3">
         <v>99400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3083700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1755300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1763100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10195600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>960000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2097800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1763100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1728600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2289400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1058000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1747500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>465500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2506400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1472100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2606900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1025900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1512100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>817900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1057100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>756500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2597500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1646400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3006900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1337400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2423800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>859500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2914100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1345100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2682700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1543900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2820700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1379200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2463800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1583500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8374,8 +8571,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8412,86 +8610,89 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>787500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>904100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>826800</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>468100</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>456400</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>299300</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>293200</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>291700</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL83" s="3">
         <v>291700</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN83" s="3">
         <v>324000</v>
       </c>
-      <c r="AN83" s="3" t="s">
+      <c r="AO83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8606,8 +8807,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8722,8 +8926,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8838,8 +9045,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8954,8 +9164,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9070,8 +9283,11 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9108,86 +9324,89 @@
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>-12307700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>-16199700</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>100979800</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>10858100</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>4416200</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>11882200</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-3436700</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>2200200</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL89" s="3">
         <v>-8094000</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN89" s="3">
         <v>4758600</v>
       </c>
-      <c r="AN89" s="3" t="s">
+      <c r="AO89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9228,8 +9447,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9266,66 +9486,66 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3">
         <v>-84000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-143000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-144000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-286300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-256800</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-158800</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-306400</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI91" s="3" t="s">
         <v>5</v>
       </c>
@@ -9344,8 +9564,11 @@
       <c r="AN91" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO91" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9460,8 +9683,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9576,8 +9802,11 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9614,86 +9843,89 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-5878000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>6743100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-8464900</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-5651400</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>2759800</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>1152100</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>4915700</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>5927500</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL94" s="3">
         <v>7260400</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN94" s="3">
         <v>4319600</v>
       </c>
-      <c r="AN94" s="3" t="s">
+      <c r="AO94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9734,8 +9966,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9772,12 +10005,12 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P96" s="3">
         <v>-3380400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -9785,11 +10018,11 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-2539000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -9797,11 +10030,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-3000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -9809,49 +10042,52 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1126600</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-2016300</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1104800</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1045700</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-1831100</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-1092800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9966,8 +10202,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10082,8 +10321,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10198,8 +10440,11 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10236,86 +10481,89 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>5149200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>5840000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-34705500</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-266200</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-4618500</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-703800</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>18202600</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-2761200</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-1668400</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-20157800</v>
       </c>
-      <c r="AN100" s="3" t="s">
+      <c r="AO100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10352,86 +10600,89 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>-558200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>-612500</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>-423900</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>172800</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-62300</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>226200</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>125700</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL101" s="3">
         <v>166100</v>
       </c>
-      <c r="AL101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN101" s="3">
         <v>851000</v>
       </c>
-      <c r="AN101" s="3" t="s">
+      <c r="AO101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10468,82 +10719,85 @@
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>-13594700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>-4229100</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>57385400</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>5113300</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>2495100</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>12328200</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>19907800</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>5492100</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="3">
         <v>-2336000</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN102" s="3">
         <v>-10228600</v>
       </c>
-      <c r="AN102" s="3" t="s">
+      <c r="AO102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
